--- a/studentport.xlsx
+++ b/studentport.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\PycharmProjects\WelcomeScreen\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -2604,7 +2604,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AG85"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2721,7 +2720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:32" s="3" customFormat="1" ht="10.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" s="3" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>0</v>
       </c>
@@ -2756,7 +2755,7 @@
       <c r="AB2" s="5"/>
       <c r="AC2" s="2"/>
     </row>
-    <row r="3" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -2847,7 +2846,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -2941,7 +2940,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -3032,7 +3031,7 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="6" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -3212,7 +3211,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -3307,7 +3306,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="9" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -3398,7 +3397,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="10" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -3679,7 +3678,7 @@
         <v>46157</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -3865,7 +3864,7 @@
         <v>46157</v>
       </c>
     </row>
-    <row r="15" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -3956,7 +3955,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="16" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -4041,7 +4040,7 @@
       <c r="AB16" s="20"/>
       <c r="AC16" s="21"/>
     </row>
-    <row r="17" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -4136,7 +4135,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="18" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>16</v>
       </c>
@@ -4227,7 +4226,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="19" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>17</v>
       </c>
@@ -4318,7 +4317,7 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="20" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>18</v>
       </c>
@@ -4409,7 +4408,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="21" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>19</v>
       </c>
@@ -4589,7 +4588,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="23" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>21</v>
       </c>
@@ -4684,7 +4683,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="24" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>22</v>
       </c>
@@ -4870,7 +4869,7 @@
         <v>46209</v>
       </c>
     </row>
-    <row r="26" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>24</v>
       </c>
@@ -4961,7 +4960,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="27" spans="1:32" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:32" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>25</v>
       </c>
@@ -5052,7 +5051,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="28" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>26</v>
       </c>
@@ -5232,7 +5231,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>28</v>
       </c>
@@ -5511,7 +5510,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>31</v>
       </c>
@@ -5602,7 +5601,7 @@
         <v>46131</v>
       </c>
     </row>
-    <row r="34" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>32</v>
       </c>
@@ -5697,7 +5696,7 @@
         <v>46246</v>
       </c>
     </row>
-    <row r="35" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>33</v>
       </c>
@@ -5792,7 +5791,7 @@
         <v>46117</v>
       </c>
     </row>
-    <row r="36" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>34</v>
       </c>
@@ -5887,7 +5886,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="37" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>35</v>
       </c>
@@ -5978,7 +5977,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="38" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>36</v>
       </c>
@@ -6069,7 +6068,7 @@
         <v>46135</v>
       </c>
     </row>
-    <row r="39" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>37</v>
       </c>
@@ -6160,7 +6159,7 @@
         <v>46209</v>
       </c>
     </row>
-    <row r="40" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>38</v>
       </c>
@@ -6522,7 +6521,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="44" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>42</v>
       </c>
@@ -6799,7 +6798,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="47" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>45</v>
       </c>
@@ -6890,7 +6889,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="48" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>46</v>
       </c>
@@ -7165,7 +7164,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="51" spans="1:33" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>49</v>
       </c>
@@ -7438,7 +7437,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="54" spans="1:33" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>52</v>
       </c>
@@ -7529,7 +7528,7 @@
         <v>46224</v>
       </c>
     </row>
-    <row r="55" spans="1:33" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>53</v>
       </c>
@@ -7614,7 +7613,7 @@
       <c r="AB55" s="42"/>
       <c r="AC55" s="15"/>
     </row>
-    <row r="56" spans="1:33" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>54</v>
       </c>
@@ -7795,7 +7794,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="58" spans="1:33" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>56</v>
       </c>
@@ -8067,7 +8066,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="61" spans="1:33" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>59</v>
       </c>
@@ -8162,7 +8161,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="62" spans="1:33" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>60</v>
       </c>
@@ -8253,7 +8252,7 @@
         <v>46135</v>
       </c>
     </row>
-    <row r="63" spans="1:33" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>61</v>
       </c>
@@ -8344,7 +8343,7 @@
         <v>46125</v>
       </c>
     </row>
-    <row r="64" spans="1:33" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>62</v>
       </c>
@@ -8435,7 +8434,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="65" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>63</v>
       </c>
@@ -8526,7 +8525,7 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="66" spans="1:32" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.35">
       <c r="AA66" s="80"/>
       <c r="AB66" s="80"/>
       <c r="AC66" s="81"/>
@@ -8846,14 +8845,7 @@
       <c r="AC85" s="83"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC66">
-    <filterColumn colId="26">
-      <filters>
-        <filter val="HE"/>
-        <filter val="SUPPLY"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AC66"/>
   <dataConsolidate/>
   <hyperlinks>
     <hyperlink ref="Z3" r:id="rId1"/>

--- a/studentport.xlsx
+++ b/studentport.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1 (5)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1 (5)'!$A$1:$AC$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1 (5)'!$A$1:$AC$65</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet1 (5)'!$A$1:$AC$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Sheet1 (5)'!$K:$K,'Sheet1 (5)'!$1:$1</definedName>
   </definedNames>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="622">
   <si>
     <t>ROLL NO.</t>
   </si>
@@ -1897,9 +1897,6 @@
   </si>
   <si>
     <t>KAYNAT26116@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -1910,16 +1907,8 @@
     <numFmt numFmtId="164" formatCode="0000\-0000\-0000"/>
     <numFmt numFmtId="165" formatCode="0;[Red]0"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -2095,210 +2084,210 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2307,21 +2296,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2604,7 +2580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG85"/>
+  <dimension ref="A1:AD65"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.1796875" customWidth="1"/>
@@ -2633,11 +2609,10 @@
     <col min="27" max="27" width="10.26953125" customWidth="1"/>
     <col min="28" max="28" width="9.1796875" customWidth="1"/>
     <col min="29" max="29" width="15" customWidth="1"/>
-    <col min="30" max="30" width="11.54296875" style="17" customWidth="1"/>
-    <col min="31" max="16384" width="9.1796875" style="17"/>
+    <col min="30" max="16384" width="9.1796875" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="3" customFormat="1" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="3" customFormat="1" ht="52.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2720,7 +2695,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:32" s="3" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" s="3" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>0</v>
       </c>
@@ -2755,7 +2730,7 @@
       <c r="AB2" s="5"/>
       <c r="AC2" s="2"/>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -2839,14 +2814,8 @@
       </c>
       <c r="AB3" s="16"/>
       <c r="AC3" s="16"/>
-      <c r="AE3" s="17">
-        <v>4465</v>
-      </c>
-      <c r="AF3" s="18">
-        <v>46148</v>
-      </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -2930,17 +2899,8 @@
       </c>
       <c r="AB4" s="20"/>
       <c r="AC4" s="21"/>
-      <c r="AD4" s="17">
-        <v>9956848055</v>
-      </c>
-      <c r="AE4" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF4" s="18">
-        <v>46143</v>
-      </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -3024,14 +2984,8 @@
       </c>
       <c r="AB5" s="20"/>
       <c r="AC5" s="21"/>
-      <c r="AE5" s="17">
-        <v>4445</v>
-      </c>
-      <c r="AF5" s="18">
-        <v>46144</v>
-      </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -3115,14 +3069,8 @@
       </c>
       <c r="AB6" s="23"/>
       <c r="AC6" s="15"/>
-      <c r="AE6" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF6" s="18">
-        <v>46121</v>
-      </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -3211,7 +3159,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -3299,14 +3247,8 @@
       <c r="AC8" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="AE8" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF8" s="18">
-        <v>46138</v>
-      </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -3390,14 +3332,8 @@
       </c>
       <c r="AB9" s="31"/>
       <c r="AC9" s="30"/>
-      <c r="AE9" s="17">
-        <v>4455</v>
-      </c>
-      <c r="AF9" s="18">
-        <v>46146</v>
-      </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -3481,14 +3417,8 @@
       </c>
       <c r="AB10" s="20"/>
       <c r="AC10" s="21"/>
-      <c r="AE10" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF10" s="18">
-        <v>46141</v>
-      </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -3576,14 +3506,8 @@
       <c r="AC11" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="AE11" s="17">
-        <v>4445</v>
-      </c>
-      <c r="AF11" s="18">
-        <v>46145</v>
-      </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -3671,14 +3595,8 @@
       <c r="AC12" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="AE12" s="17">
-        <v>4510</v>
-      </c>
-      <c r="AF12" s="18">
-        <v>46157</v>
-      </c>
     </row>
-    <row r="13" spans="1:32" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:29" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -3762,14 +3680,8 @@
       </c>
       <c r="AB13" s="16"/>
       <c r="AC13" s="16"/>
-      <c r="AE13" s="17">
-        <v>4505</v>
-      </c>
-      <c r="AF13" s="18">
-        <v>46156</v>
-      </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -3857,14 +3769,8 @@
       <c r="AC14" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="AE14" s="17">
-        <v>4510</v>
-      </c>
-      <c r="AF14" s="18">
-        <v>46157</v>
-      </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -3948,14 +3854,8 @@
       </c>
       <c r="AB15" s="23"/>
       <c r="AC15" s="15"/>
-      <c r="AE15" s="17">
-        <v>4455</v>
-      </c>
-      <c r="AF15" s="18">
-        <v>46146</v>
-      </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -4040,7 +3940,7 @@
       <c r="AB16" s="20"/>
       <c r="AC16" s="21"/>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -4128,14 +4028,8 @@
       <c r="AC17" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="AE17" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF17" s="18">
-        <v>46142</v>
-      </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>16</v>
       </c>
@@ -4219,14 +4113,8 @@
       </c>
       <c r="AB18" s="16"/>
       <c r="AC18" s="16"/>
-      <c r="AE18" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF18" s="18">
-        <v>46136</v>
-      </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>17</v>
       </c>
@@ -4310,14 +4198,8 @@
       </c>
       <c r="AB19" s="31"/>
       <c r="AC19" s="30"/>
-      <c r="AE19" s="17">
-        <v>4445</v>
-      </c>
-      <c r="AF19" s="18">
-        <v>46144</v>
-      </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>18</v>
       </c>
@@ -4401,14 +4283,8 @@
       </c>
       <c r="AB20" s="16"/>
       <c r="AC20" s="16"/>
-      <c r="AE20" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF20" s="18">
-        <v>46142</v>
-      </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>19</v>
       </c>
@@ -4492,14 +4368,8 @@
       </c>
       <c r="AB21" s="23"/>
       <c r="AC21" s="27"/>
-      <c r="AE21" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF21" s="18">
-        <v>46142</v>
-      </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>20</v>
       </c>
@@ -4588,7 +4458,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>21</v>
       </c>
@@ -4676,14 +4546,8 @@
       <c r="AC23" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="AE23" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF23" s="18">
-        <v>46124</v>
-      </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>22</v>
       </c>
@@ -4767,14 +4631,8 @@
       </c>
       <c r="AB24" s="20"/>
       <c r="AC24" s="21"/>
-      <c r="AE24" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF24" s="18">
-        <v>46128</v>
-      </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>23</v>
       </c>
@@ -4862,14 +4720,8 @@
       <c r="AC25" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="AE25" s="17">
-        <v>4780</v>
-      </c>
-      <c r="AF25" s="18">
-        <v>46209</v>
-      </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>24</v>
       </c>
@@ -4953,14 +4805,8 @@
       </c>
       <c r="AB26" s="23"/>
       <c r="AC26" s="27"/>
-      <c r="AE26" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF26" s="18">
-        <v>46121</v>
-      </c>
     </row>
-    <row r="27" spans="1:32" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:29" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>25</v>
       </c>
@@ -5044,14 +4890,8 @@
       </c>
       <c r="AB27" s="23"/>
       <c r="AC27" s="27"/>
-      <c r="AE27" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF27" s="18">
-        <v>46139</v>
-      </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>26</v>
       </c>
@@ -5135,14 +4975,8 @@
       </c>
       <c r="AB28" s="23"/>
       <c r="AC28" s="27"/>
-      <c r="AE28" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF28" s="18">
-        <v>46142</v>
-      </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>27</v>
       </c>
@@ -5231,7 +5065,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>28</v>
       </c>
@@ -5319,14 +5153,8 @@
       <c r="AC30" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="AE30" s="17">
-        <v>4510</v>
-      </c>
-      <c r="AF30" s="18">
-        <v>46157</v>
-      </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>29</v>
       </c>
@@ -5414,14 +5242,8 @@
       <c r="AC31" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="AE31" s="17">
-        <v>4470</v>
-      </c>
-      <c r="AF31" s="18">
-        <v>46149</v>
-      </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
         <v>30</v>
       </c>
@@ -5510,7 +5332,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>31</v>
       </c>
@@ -5594,14 +5416,8 @@
       </c>
       <c r="AB33" s="63"/>
       <c r="AC33" s="27"/>
-      <c r="AE33" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF33" s="18">
-        <v>46131</v>
-      </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>32</v>
       </c>
@@ -5689,14 +5505,8 @@
       <c r="AC34" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="AE34" s="17">
-        <v>4955</v>
-      </c>
-      <c r="AF34" s="18">
-        <v>46246</v>
-      </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>33</v>
       </c>
@@ -5784,14 +5594,8 @@
       <c r="AC35" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="AE35" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF35" s="18">
-        <v>46117</v>
-      </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>34</v>
       </c>
@@ -5879,14 +5683,8 @@
       <c r="AC36" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="AE36" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF36" s="18">
-        <v>46130</v>
-      </c>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>35</v>
       </c>
@@ -5970,14 +5768,8 @@
       </c>
       <c r="AB37" s="65"/>
       <c r="AC37" s="21"/>
-      <c r="AE37" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF37" s="18">
-        <v>46143</v>
-      </c>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>36</v>
       </c>
@@ -6061,14 +5853,8 @@
       </c>
       <c r="AB38" s="20"/>
       <c r="AC38" s="21"/>
-      <c r="AE38" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF38" s="18">
-        <v>46135</v>
-      </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>37</v>
       </c>
@@ -6152,14 +5938,8 @@
       </c>
       <c r="AB39" s="66"/>
       <c r="AC39" s="16"/>
-      <c r="AE39" s="17">
-        <v>4770</v>
-      </c>
-      <c r="AF39" s="18">
-        <v>46209</v>
-      </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>38</v>
       </c>
@@ -6247,14 +6027,8 @@
       <c r="AC40" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="AE40" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF40" s="18">
-        <v>46139</v>
-      </c>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>39</v>
       </c>
@@ -6343,7 +6117,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>40</v>
       </c>
@@ -6432,7 +6206,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>41</v>
       </c>
@@ -6521,7 +6295,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>42</v>
       </c>
@@ -6609,14 +6383,8 @@
       <c r="AC44" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="AE44" s="17">
-        <v>4520</v>
-      </c>
-      <c r="AF44" s="18">
-        <v>46155</v>
-      </c>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>43</v>
       </c>
@@ -6700,14 +6468,8 @@
       </c>
       <c r="AB45" s="16"/>
       <c r="AC45" s="31"/>
-      <c r="AE45" s="17">
-        <v>4450</v>
-      </c>
-      <c r="AF45" s="18">
-        <v>46145</v>
-      </c>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>44</v>
       </c>
@@ -6791,14 +6553,8 @@
       </c>
       <c r="AB46" s="42"/>
       <c r="AC46" s="15"/>
-      <c r="AE46" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF46" s="18">
-        <v>46142</v>
-      </c>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>45</v>
       </c>
@@ -6882,14 +6638,8 @@
       </c>
       <c r="AB47" s="15"/>
       <c r="AC47" s="16"/>
-      <c r="AE47" s="17">
-        <v>4530</v>
-      </c>
-      <c r="AF47" s="18">
-        <v>46161</v>
-      </c>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>46</v>
       </c>
@@ -6977,14 +6727,8 @@
       <c r="AC48" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="AE48" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF48" s="18">
-        <v>46142</v>
-      </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>47</v>
       </c>
@@ -7068,14 +6812,8 @@
       </c>
       <c r="AB49" s="15"/>
       <c r="AC49" s="16"/>
-      <c r="AE49" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF49" s="18">
-        <v>46116</v>
-      </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>48</v>
       </c>
@@ -7164,7 +6902,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>49</v>
       </c>
@@ -7252,14 +6990,8 @@
       <c r="AC51" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="AE51" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF51" s="18">
-        <v>46136</v>
-      </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>50</v>
       </c>
@@ -7348,7 +7080,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>51</v>
       </c>
@@ -7437,7 +7169,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>52</v>
       </c>
@@ -7521,14 +7253,8 @@
       </c>
       <c r="AB54" s="42"/>
       <c r="AC54" s="15"/>
-      <c r="AE54" s="17">
-        <v>4845</v>
-      </c>
-      <c r="AF54" s="18">
-        <v>46224</v>
-      </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>53</v>
       </c>
@@ -7613,7 +7339,7 @@
       <c r="AB55" s="42"/>
       <c r="AC55" s="15"/>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>54</v>
       </c>
@@ -7697,15 +7423,9 @@
       </c>
       <c r="AB56" s="42"/>
       <c r="AC56" s="15"/>
-      <c r="AE56" s="17">
-        <v>4490</v>
-      </c>
-      <c r="AF56" s="18">
-        <v>46151</v>
-      </c>
-      <c r="AG56" s="18"/>
+      <c r="AD56" s="18"/>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>55</v>
       </c>
@@ -7794,7 +7514,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>56</v>
       </c>
@@ -7878,15 +7598,9 @@
       </c>
       <c r="AB58" s="42"/>
       <c r="AC58" s="15"/>
-      <c r="AE58" s="17">
-        <v>4470</v>
-      </c>
-      <c r="AF58" s="18">
-        <v>46149</v>
-      </c>
-      <c r="AG58" s="18"/>
+      <c r="AD58" s="18"/>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>57</v>
       </c>
@@ -7975,7 +7689,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>58</v>
       </c>
@@ -8059,14 +7773,8 @@
       </c>
       <c r="AB60" s="25"/>
       <c r="AC60" s="15"/>
-      <c r="AE60" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF60" s="18">
-        <v>46136</v>
-      </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>59</v>
       </c>
@@ -8154,14 +7862,8 @@
       <c r="AC61" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="AE61" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF61" s="18">
-        <v>46130</v>
-      </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>60</v>
       </c>
@@ -8245,14 +7947,8 @@
       </c>
       <c r="AB62" s="42"/>
       <c r="AC62" s="15"/>
-      <c r="AE62" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF62" s="18">
-        <v>46135</v>
-      </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>61</v>
       </c>
@@ -8336,14 +8032,8 @@
       </c>
       <c r="AB63" s="42"/>
       <c r="AC63" s="15"/>
-      <c r="AE63" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF63" s="18">
-        <v>46125</v>
-      </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>62</v>
       </c>
@@ -8427,14 +8117,8 @@
       </c>
       <c r="AB64" s="42"/>
       <c r="AC64" s="15"/>
-      <c r="AE64" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF64" s="18">
-        <v>46142</v>
-      </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>63</v>
       </c>
@@ -8518,334 +8202,9 @@
       </c>
       <c r="AB65" s="42"/>
       <c r="AC65" s="15"/>
-      <c r="AE65" s="17">
-        <v>4435</v>
-      </c>
-      <c r="AF65" s="18">
-        <v>46140</v>
-      </c>
-    </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="AA66" s="80"/>
-      <c r="AB66" s="80"/>
-      <c r="AC66" s="81"/>
-      <c r="AE66" s="17">
-        <f>SUM(AE3:AE65)</f>
-        <v>219640</v>
-      </c>
-    </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="AA67" s="82"/>
-      <c r="AB67" s="82"/>
-      <c r="AC67" s="82"/>
-    </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="K68">
-        <v>119745</v>
-      </c>
-      <c r="Q68" s="83"/>
-      <c r="R68" s="83"/>
-      <c r="S68" s="83"/>
-      <c r="T68" s="83"/>
-      <c r="U68" s="83"/>
-      <c r="V68" s="83"/>
-      <c r="W68" s="83"/>
-      <c r="X68" s="83"/>
-      <c r="Y68" s="83"/>
-      <c r="Z68" s="83"/>
-      <c r="AA68" s="82"/>
-      <c r="AB68" s="82"/>
-      <c r="AC68" s="82"/>
-    </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="Q69" s="83"/>
-      <c r="R69" s="83"/>
-      <c r="S69" s="83"/>
-      <c r="T69" s="83"/>
-      <c r="U69" s="83"/>
-      <c r="V69" s="83"/>
-      <c r="W69" s="83"/>
-      <c r="X69" s="83"/>
-      <c r="Y69" s="83"/>
-      <c r="Z69" s="83"/>
-      <c r="AA69" s="82"/>
-      <c r="AB69" s="82"/>
-      <c r="AC69" s="82"/>
-    </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="Q70" s="83"/>
-      <c r="R70" s="83"/>
-      <c r="S70" s="83"/>
-      <c r="T70" s="83"/>
-      <c r="U70" s="83"/>
-      <c r="V70" s="83"/>
-      <c r="W70" s="83"/>
-      <c r="X70" s="83"/>
-      <c r="Y70" s="83"/>
-      <c r="Z70" s="83"/>
-      <c r="AA70" s="82"/>
-      <c r="AB70" s="82"/>
-      <c r="AC70" s="82"/>
-    </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="Q71" s="83"/>
-      <c r="R71" s="83"/>
-      <c r="S71" s="83"/>
-      <c r="T71" s="83"/>
-      <c r="U71" s="83"/>
-      <c r="V71" s="83"/>
-      <c r="W71" s="83"/>
-      <c r="X71" s="83"/>
-      <c r="Y71" s="83"/>
-      <c r="Z71" s="83"/>
-      <c r="AA71" s="82"/>
-      <c r="AB71" s="82"/>
-      <c r="AC71" s="82"/>
-    </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="Q72" s="83"/>
-      <c r="R72" s="83"/>
-      <c r="S72" s="83"/>
-      <c r="T72" s="83"/>
-      <c r="U72" s="83"/>
-      <c r="V72" s="83"/>
-      <c r="W72" s="83"/>
-      <c r="X72" s="83"/>
-      <c r="Y72" s="83"/>
-      <c r="Z72" s="83"/>
-      <c r="AA72" s="82"/>
-      <c r="AB72" s="82"/>
-      <c r="AC72" s="82"/>
-    </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="Q73" s="83"/>
-      <c r="R73" s="83"/>
-      <c r="S73" s="83"/>
-      <c r="T73" s="83"/>
-      <c r="U73" s="83"/>
-      <c r="V73" s="83"/>
-      <c r="W73" s="83"/>
-      <c r="X73" s="83"/>
-      <c r="Y73" s="83"/>
-      <c r="Z73" s="83"/>
-      <c r="AA73" s="80"/>
-      <c r="AB73" s="80"/>
-      <c r="AC73" s="80"/>
-    </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="Q74" s="83"/>
-      <c r="R74" s="83"/>
-      <c r="S74" s="83"/>
-      <c r="T74" s="83"/>
-      <c r="U74" s="83"/>
-      <c r="V74" s="83"/>
-      <c r="W74" s="83"/>
-      <c r="X74" s="83"/>
-      <c r="Y74" s="83"/>
-      <c r="Z74" s="83"/>
-      <c r="AA74" s="82"/>
-      <c r="AB74" s="82"/>
-      <c r="AC74" s="83"/>
-    </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="Q75" s="83"/>
-      <c r="R75" s="83"/>
-      <c r="S75" s="83"/>
-      <c r="T75" s="83"/>
-      <c r="U75" s="83"/>
-      <c r="V75" s="83"/>
-      <c r="W75" s="83"/>
-      <c r="X75" s="83"/>
-      <c r="Y75" s="83"/>
-      <c r="Z75" s="83"/>
-      <c r="AA75" s="82"/>
-      <c r="AB75" s="82"/>
-      <c r="AC75" s="82"/>
-    </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="Q76" s="83"/>
-      <c r="R76" s="83"/>
-      <c r="S76" s="83"/>
-      <c r="T76" s="83"/>
-      <c r="U76" s="83"/>
-      <c r="V76" s="83"/>
-      <c r="W76" s="83"/>
-      <c r="X76" s="83"/>
-      <c r="Y76" s="83"/>
-      <c r="Z76" s="83"/>
-      <c r="AA76" s="84" t="s">
-        <v>133</v>
-      </c>
-      <c r="AB76" s="84" t="s">
-        <v>397</v>
-      </c>
-      <c r="AC76" s="84" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="Q77" s="83"/>
-      <c r="R77" s="83"/>
-      <c r="S77" s="83"/>
-      <c r="T77" s="83"/>
-      <c r="U77" s="83"/>
-      <c r="V77" s="83"/>
-      <c r="W77" s="83"/>
-      <c r="X77" s="83"/>
-      <c r="Y77" s="83"/>
-      <c r="Z77" s="83"/>
-      <c r="AA77" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB77" s="78">
-        <v>2</v>
-      </c>
-      <c r="AC77" s="78">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="Q78" s="83"/>
-      <c r="R78" s="83"/>
-      <c r="S78" s="83"/>
-      <c r="T78" s="83"/>
-      <c r="U78" s="83"/>
-      <c r="V78" s="83"/>
-      <c r="W78" s="83"/>
-      <c r="X78" s="83"/>
-      <c r="Y78" s="83"/>
-      <c r="Z78" s="83"/>
-      <c r="AA78" s="84" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB78" s="78">
-        <v>1</v>
-      </c>
-      <c r="AC78" s="78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="Q79" s="83"/>
-      <c r="R79" s="83"/>
-      <c r="S79" s="83"/>
-      <c r="T79" s="83"/>
-      <c r="U79" s="83"/>
-      <c r="V79" s="83"/>
-      <c r="W79" s="83"/>
-      <c r="X79" s="83"/>
-      <c r="Y79" s="83"/>
-      <c r="Z79" s="83"/>
-      <c r="AA79" s="84" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB79" s="78"/>
-      <c r="AC79" s="78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="Q80" s="83"/>
-      <c r="R80" s="83"/>
-      <c r="S80" s="83"/>
-      <c r="T80" s="83"/>
-      <c r="U80" s="83"/>
-      <c r="V80" s="83"/>
-      <c r="W80" s="83"/>
-      <c r="X80" s="83"/>
-      <c r="Y80" s="83"/>
-      <c r="Z80" s="83"/>
-      <c r="AA80" s="84" t="s">
-        <v>170</v>
-      </c>
-      <c r="AB80" s="78"/>
-      <c r="AC80" s="78"/>
-    </row>
-    <row r="81" spans="17:29" x14ac:dyDescent="0.35">
-      <c r="Q81" s="83"/>
-      <c r="R81" s="83"/>
-      <c r="S81" s="83"/>
-      <c r="T81" s="83"/>
-      <c r="U81" s="83"/>
-      <c r="V81" s="83"/>
-      <c r="W81" s="83"/>
-      <c r="X81" s="83"/>
-      <c r="Y81" s="83"/>
-      <c r="Z81" s="83"/>
-      <c r="AA81" s="84" t="s">
-        <v>622</v>
-      </c>
-      <c r="AB81" s="78">
-        <f>SUBTOTAL(9,AB77:AB80)</f>
-        <v>3</v>
-      </c>
-      <c r="AC81" s="78">
-        <f>SUBTOTAL(9,AC77:AC80)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="17:29" x14ac:dyDescent="0.35">
-      <c r="Q82" s="83"/>
-      <c r="R82" s="83"/>
-      <c r="S82" s="83"/>
-      <c r="T82" s="83"/>
-      <c r="U82" s="83"/>
-      <c r="V82" s="83"/>
-      <c r="W82" s="83"/>
-      <c r="X82" s="83"/>
-      <c r="Y82" s="83"/>
-      <c r="Z82" s="83"/>
-      <c r="AA82" s="83"/>
-      <c r="AB82" s="83"/>
-      <c r="AC82" s="83"/>
-    </row>
-    <row r="83" spans="17:29" x14ac:dyDescent="0.35">
-      <c r="Q83" s="83"/>
-      <c r="R83" s="83"/>
-      <c r="S83" s="83"/>
-      <c r="T83" s="83"/>
-      <c r="U83" s="83"/>
-      <c r="V83" s="83"/>
-      <c r="W83" s="83"/>
-      <c r="X83" s="83"/>
-      <c r="Y83" s="83"/>
-      <c r="Z83" s="83"/>
-      <c r="AA83" s="83"/>
-      <c r="AB83" s="83"/>
-      <c r="AC83" s="83"/>
-    </row>
-    <row r="84" spans="17:29" x14ac:dyDescent="0.35">
-      <c r="Q84" s="83"/>
-      <c r="R84" s="83"/>
-      <c r="S84" s="83"/>
-      <c r="T84" s="83"/>
-      <c r="U84" s="83"/>
-      <c r="V84" s="83"/>
-      <c r="W84" s="83"/>
-      <c r="X84" s="83"/>
-      <c r="Y84" s="83"/>
-      <c r="Z84" s="83"/>
-      <c r="AA84" s="83"/>
-      <c r="AB84" s="83"/>
-      <c r="AC84" s="83"/>
-    </row>
-    <row r="85" spans="17:29" x14ac:dyDescent="0.35">
-      <c r="Q85" s="83"/>
-      <c r="R85" s="83"/>
-      <c r="S85" s="83"/>
-      <c r="T85" s="83"/>
-      <c r="U85" s="83"/>
-      <c r="V85" s="83"/>
-      <c r="W85" s="83"/>
-      <c r="X85" s="83"/>
-      <c r="Y85" s="83"/>
-      <c r="Z85" s="83"/>
-      <c r="AA85" s="83"/>
-      <c r="AB85" s="83"/>
-      <c r="AC85" s="83"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC66"/>
+  <autoFilter ref="A1:AC65"/>
   <dataConsolidate/>
   <hyperlinks>
     <hyperlink ref="Z3" r:id="rId1"/>
